--- a/out/MLP-mamba2_repeat_3_000007.xlsx
+++ b/out/MLP-mamba2_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002907415414252319</v>
+        <v>-0.0002558379968549125</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.35182057490637</v>
+        <v>2.949434255239926</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.708822459522691</v>
+        <v>5.903427803557751</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5026204242363479</v>
+        <v>0.4422808233376368</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.357744174259253</v>
+        <v>3.834596648527906</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6284390724051092</v>
+        <v>0.5529948813046265</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.11208178266461</v>
+        <v>4.498375938655091</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9008644299822252</v>
+        <v>0.7927155398263401</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.285726438394549</v>
+        <v>5.53112442867748</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.963746497048326</v>
+        <v>0.8480486066904452</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.312422540668464</v>
+        <v>6.434565577004671</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.021377772514616</v>
+        <v>0.8987613287251282</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.391503819269747</v>
+        <v>7.384103103526692</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4609287923607993</v>
+        <v>0.4055942717942126</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.291134870605699</v>
+        <v>7.295783451296595</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.222607539249372</v>
+        <v>0.1958828518027796</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.275059725587498</v>
+        <v>7.281638129078038</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.106065252108452</v>
+        <v>0.09333295997584183</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.264407136028597</v>
+        <v>7.272264351739246</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03142639434499839</v>
+        <v>0.02765354180644621</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.221081192922055</v>
+        <v>7.234139785081767</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02078738795269658</v>
+        <v>0.01829178669006932</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.231213400391701</v>
+        <v>7.243055612526054</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0106374585501774</v>
+        <v>0.009360284807746713</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.231687254675283</v>
+        <v>7.243471980747767</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00543902883938501</v>
+        <v>0.00478570511217331</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.231921545647701</v>
+        <v>7.243677535027578</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002041616816062795</v>
+        <v>0.001795629217978324</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.230561375930506</v>
+        <v>7.242480216228637</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001110408081253631</v>
+        <v>0.0009767571129377368</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.2307395033668</v>
+        <v>7.242636340849742</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005322374465774301</v>
+        <v>0.0004678643205822054</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.230692834567961</v>
+        <v>7.242594691590229</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003275768296930436</v>
+        <v>0.000287234669878207</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.230815689015468</v>
+        <v>7.242702060047218</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001689633876150413</v>
+        <v>0.0001483760044653323</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.230825891199796</v>
+        <v>7.242710423068776</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>6.893289167810316e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.230815634721205</v>
+        <v>7.242700816527956</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.872414786603389e-05</v>
+        <v>4.232841597722033e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.230834402638209</v>
+        <v>7.242716788310757</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>1.7146614275097e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.230824485023604</v>
+        <v>7.242707441886049</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.230816470318388</v>
+        <v>7.242699838903246</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.230812380505899</v>
+        <v>7.242695665731654</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.230806513063214</v>
+        <v>7.242689943452624</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.901262215535431</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.230801443707847</v>
+        <v>7.242684874097255</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.230797078733879</v>
+        <v>7.242680509123287</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.230798169980334</v>
+        <v>7.242681600369743</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.230797480373198</v>
+        <v>7.242680910762608</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.2307975106856</v>
+        <v>7.242680941075009</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.230797321233091</v>
+        <v>7.242680751622499</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.230797374279794</v>
+        <v>7.242680804669202</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.230797427326495</v>
+        <v>7.242680857715905</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.230797389435994</v>
+        <v>7.242680819825402</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.230797260608288</v>
+        <v>7.242680690997696</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.23079711662438</v>
+        <v>7.242680547013788</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.230797010530974</v>
+        <v>7.242680440920383</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.230796775609862</v>
+        <v>7.242680205999271</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.230796942328071</v>
+        <v>7.242680372717479</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.23079713935868</v>
+        <v>7.24268056974809</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.230796980218573</v>
+        <v>7.242680410607981</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.230797018109074</v>
+        <v>7.242680448498483</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.230797215139685</v>
+        <v>7.242680645529093</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.230797192405385</v>
+        <v>7.242680622794792</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.230797040843376</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.230796965062373</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.230797063577675</v>
+        <v>7.242680493967086</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.901262215535431</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.230797071155777</v>
+        <v>7.242680501545186</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.230797336389291</v>
+        <v>7.2426807667787</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.230797040843376</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.50126221553543</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.230797283342589</v>
+        <v>7.242680713731997</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.230797366701692</v>
+        <v>7.242680797091102</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.230797199983483</v>
+        <v>7.242680630372893</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.230797389435994</v>
+        <v>7.242680819825402</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.230797040843376</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.230796836234665</v>
+        <v>7.242680266624074</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.23079694990617</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.230796965062373</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.230796730141259</v>
+        <v>7.242680160530669</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.230796790766062</v>
+        <v>7.242680221155471</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.230796661938356</v>
+        <v>7.242680092327764</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.230796798344164</v>
+        <v>7.242680228733573</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.230796972640471</v>
+        <v>7.242680403029881</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.23079711662438</v>
+        <v>7.242680547013788</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.23079694990617</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.230796942328071</v>
+        <v>7.242680372717479</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.230796654360255</v>
+        <v>7.242680084749664</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.50126221553543</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.230796669516455</v>
+        <v>7.242680099905865</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.230796896859468</v>
+        <v>7.242680327248877</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.50126221553543</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.230796881703267</v>
+        <v>7.242680312092676</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.230796987796673</v>
+        <v>7.242680418186081</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.230796714985058</v>
+        <v>7.242680145374468</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.230796813500364</v>
+        <v>7.242680243889772</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.230796965062373</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.230796980218573</v>
+        <v>7.242680410607981</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.901262215535431</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.230797040843376</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.8241370729394371</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.23079713935868</v>
+        <v>7.24268056974809</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.230796972640471</v>
+        <v>7.242680403029881</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.23079692717187</v>
+        <v>7.242680357561278</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.23079691201567</v>
+        <v>7.242680342405078</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.23079694990617</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.230796965062373</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.230796957484271</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000007.xlsx
+++ b/out/MLP-mamba2_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.4094390911976031</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002907415414252319</v>
+        <v>-0.0001195301987472922</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.35182057490637</v>
+        <v>1.378006581113772</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.708822459522691</v>
+        <v>2.758143463270271</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5026204242363479</v>
+        <v>0.2066382565065231</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.357744174259253</v>
+        <v>1.791563769274833</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6284390724051092</v>
+        <v>0.258365056373643</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.11208178266461</v>
+        <v>2.1016884411118</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9008644299822252</v>
+        <v>0.3703649203658247</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.285726438394549</v>
+        <v>2.584199357910645</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.963746497048326</v>
+        <v>0.3962174510474997</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.312422540668464</v>
+        <v>3.006296628056957</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.021377772514616</v>
+        <v>0.4199106367843176</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.391503819269747</v>
+        <v>3.449930432348518</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4609287923607993</v>
+        <v>0.1894978605574462</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.291134870605699</v>
+        <v>3.408666572608229</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.222607539249372</v>
+        <v>0.09151816219497087</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.275059725587498</v>
+        <v>3.402057731525406</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.106065252108452</v>
+        <v>0.04360629251232053</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.264407136028597</v>
+        <v>3.397678188899879</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03142639434499839</v>
+        <v>0.012919192335016</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.221081192922055</v>
+        <v>3.379864880079196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02078738795269658</v>
+        <v>0.008543379330265661</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.231213400391701</v>
+        <v>3.384028011287432</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0106374585501774</v>
+        <v>0.004370648407233624</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.231687254675283</v>
+        <v>3.384219882949752</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00543902883938501</v>
+        <v>0.002232809931574127</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.231921545647701</v>
+        <v>3.384313258733858</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002041616816062795</v>
+        <v>0.0008366560279074807</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.230561375930506</v>
+        <v>3.38375105805355</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001110408081253631</v>
+        <v>0.000453703323355783</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.2307395033668</v>
+        <v>3.383821339809293</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005322374465774301</v>
+        <v>0.0002159349262552153</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.230692834567961</v>
+        <v>3.383799216289723</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003275768296930436</v>
+        <v>0.0001317697613234706</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.230815689015468</v>
+        <v>3.383846717574648</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001689633876150413</v>
+        <v>6.602647186649616e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.230825891199796</v>
+        <v>3.383847951288133</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>2.996825957748122e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.230815634721205</v>
+        <v>3.383840786855772</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.872414786603389e-05</v>
+        <v>1.67454884219661e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.230834402638209</v>
+        <v>3.38384557410177</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.230824485023604</v>
+        <v>3.383838515269014</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.230816470318388</v>
+        <v>3.383832282606765</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.230812380505899</v>
+        <v>3.383827696697232</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.230806513063214</v>
+        <v>3.383822263565764</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.230801443707847</v>
+        <v>3.383817216944697</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.230797078733879</v>
+        <v>3.383817535224913</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.230798169980334</v>
+        <v>3.38381862647137</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.230797480373198</v>
+        <v>3.383817936864233</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.2307975106856</v>
+        <v>3.383817967176636</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.230797321233091</v>
+        <v>3.383817777724126</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.230797374279794</v>
+        <v>3.383817830770829</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.230797427326495</v>
+        <v>3.383817883817531</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.230797389435994</v>
+        <v>3.383817845927029</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.230797260608288</v>
+        <v>3.383817717099322</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.23079711662438</v>
+        <v>3.383817573115415</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.230797010530974</v>
+        <v>3.383817467022009</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.230796775609862</v>
+        <v>3.383817232100898</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.230796942328071</v>
+        <v>3.383817398819106</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.23079713935868</v>
+        <v>3.383817595849716</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.230796980218573</v>
+        <v>3.383817436709608</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.230797018109074</v>
+        <v>3.383817474600109</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.230797215139685</v>
+        <v>3.38381767163072</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.230797192405385</v>
+        <v>3.383817648896418</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.230797040843376</v>
+        <v>3.383817497334411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.230796965062373</v>
+        <v>3.383817421553407</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.230797063577675</v>
+        <v>3.383817520068713</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.230797071155777</v>
+        <v>3.383817527646813</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.230797336389291</v>
+        <v>3.383817792880326</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.230797040843376</v>
+        <v>3.383817497334411</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.230797283342589</v>
+        <v>3.383817739833623</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.230797366701692</v>
+        <v>3.383817823192728</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.230797199983483</v>
+        <v>3.38381765647452</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.230797389435994</v>
+        <v>3.383817845927029</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.230797040843376</v>
+        <v>3.383817497334411</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.230796836234665</v>
+        <v>3.3838172927257</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.23079694990617</v>
+        <v>3.383817406397206</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.230796965062373</v>
+        <v>3.383817421553407</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.230796730141259</v>
+        <v>3.383817186632295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.230796790766062</v>
+        <v>3.383817247257098</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.230796661938356</v>
+        <v>3.383817118429391</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.230796798344164</v>
+        <v>3.383817254835199</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.230796972640471</v>
+        <v>3.383817429131507</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.23079711662438</v>
+        <v>3.383817573115415</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.23079694990617</v>
+        <v>3.383817406397206</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.230796942328071</v>
+        <v>3.383817398819106</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.230796654360255</v>
+        <v>3.38381711085129</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.50126221553543</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.230796669516455</v>
+        <v>3.383817126007492</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.230796896859468</v>
+        <v>3.383817353350503</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.230796881703267</v>
+        <v>3.383817338194302</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.230796987796673</v>
+        <v>3.383817444287708</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.230796714985058</v>
+        <v>3.383817171476094</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.230796813500364</v>
+        <v>3.383817269991399</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.230796965062373</v>
+        <v>3.383817421553407</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.230796980218573</v>
+        <v>3.383817436709608</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.230797040843376</v>
+        <v>3.383817497334411</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.23079713935868</v>
+        <v>3.383817595849716</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.230796972640471</v>
+        <v>3.383817429131507</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.23079692717187</v>
+        <v>3.383817383662905</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.23079691201567</v>
+        <v>3.383817368506704</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.23079694990617</v>
+        <v>3.383817406397206</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.230796965062373</v>
+        <v>3.383817421553407</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.230796957484271</v>
+        <v>3.383817413975307</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000007.xlsx
+++ b/out/MLP-mamba2_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3334150016307831</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4094390911976031</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5003138184547424</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4284367263317108</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.2124502211809158</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4235819280147552</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.3893640637397766</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3644724190235138</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2540276944637299</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4570061266422272</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3272684812545776</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3567812442779541</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3465485274791718</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5172564387321472</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2441475838422775</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2246038317680359</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3207010328769684</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4505587654005176</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4666726589202881</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.3124177157878876</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3402253091335297</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.6286754608154297</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.6563650369644165</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.669436947795724</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.757672905921936</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3467929661273956</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4322807192802429</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4422162175178528</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3769911527633667</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3560411334037781</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.6990740299224854</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3389512896537781</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4465124011039734</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4007908701896667</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2456454634666443</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4793564677238464</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5146462321281433</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.7677150964736938</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.9504247903823853</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4715000987052917</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.6933432221412659</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001195301987472922</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.378006581113772</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2600908875465393</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.758143463270271</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2066382565065231</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5216060280799866</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.791563769274833</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.258365056373643</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6386104822158813</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.1016884411118</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3703649203658247</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8743221759796143</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.669436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.584199357910645</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.3962174510474997</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9118449687957764</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.006296628056957</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4199106367843176</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8282283544540405</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.449930432348518</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1894978605574462</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.607400119304657</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9627717100636436</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.408666572608229</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.09151816219497087</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.03757831454277039</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.402057731525406</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04360629251232053</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.128441646695137</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.397678188899879</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.012919192335016</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.2431824505329132</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.379864880079196</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008543379330265661</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3690527975559235</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.384028011287432</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004370648407233624</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.09341432154178619</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.384219882949752</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002232809931574127</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2534955739974976</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.384313258733858</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008366560279074807</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.3762439489364624</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.38375105805355</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000453703323355783</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3615978062152863</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.383821339809293</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002159349262552153</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.651965320110321</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.383799216289723</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001317697613234706</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5263922810554504</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.383846717574648</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.602647186649616e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2178253084421158</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.383847951288133</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.996825957748122e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9727963805198669</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.256106472331563</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.383840786855772</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.67454884219661e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.1924462020397186</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.38384557410177</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.06199027970433235</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.383838515269014</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3139770328998566</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.383832282606765</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.133549302816391</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.383827696697232</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.2581522166728973</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.383822263565764</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.8350391387939453</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7627717100636433</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.383817216944697</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9504045844078064</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.669436947795724</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.383817535224913</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9551312327384949</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.38381862647137</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.05566310882568359</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.383817936864233</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.02230958081781864</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.383817967176636</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.0681685134768486</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.383817777724126</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.1748306006193161</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.383817830770829</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1063151508569717</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.383817883817531</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1628269851207733</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.383817845927029</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1530886441469193</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.383817717099322</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.1904149502515793</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.383817573115415</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3484366834163666</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2932034134864807</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.383817467022009</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3553952276706696</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.127453550696373</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.7941673398017883</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.383817232100898</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.7187919616699219</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.383817398819106</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.1111945584416389</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.383817595849716</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3716713190078735</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.383817436709608</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6931749582290649</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.383817474600109</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.520207405090332</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.38381767163072</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1533606052398682</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.383817648896418</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2409333139657974</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.383817497334411</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4776118397712708</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.383817421553407</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3957023322582245</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.383817520068713</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.673356831073761</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.383817527646813</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2536543607711792</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.383817792880326</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5524531006813049</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.383817497334411</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.6545088291168213</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.383817739833623</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.08413980156183243</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.383817823192728</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.8305273056030273</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.38381765647452</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.05593381449580193</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.383817845927029</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.1374646872282028</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.383817497334411</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2275641262531281</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.3838172927257</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3994114995002747</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.383817406397206</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1130324229598045</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.383817421553407</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4539130926132202</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.383817186632295</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.1283512562513351</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.383817247257098</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6326693296432495</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.383817118429391</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.883162796497345</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.383817254835199</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4758367538452148</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.383817429131507</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1619477570056915</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.383817573115415</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3882326483726501</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.383817406397206</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.04950717091560364</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.383817398819106</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3260453045368195</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.38381711085129</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.7767101526260376</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.383817126007492</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3583757877349854</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.383817353350503</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.7261248230934143</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.383817338194302</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.06479696929454803</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.383817444287708</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4512325525283813</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.383817171476094</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7126254439353943</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.383817269991399</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4403885900974274</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.383817421553407</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4690607786178589</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.383817436709608</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4713209569454193</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.5369348526000977</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.383817497334411</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2627516686916351</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.383817595849716</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2114299237728119</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.383817429131507</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3735687136650085</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3009952008724213</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.383817383662905</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4682797491550446</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.383817368506704</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.423176109790802</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.383817406397206</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4014048874378204</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.383817421553407</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3826521039009094</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.383817413975307</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000007.xlsx
+++ b/out/MLP-mamba2_repeat_3_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.3334150016307831</v>
+        <v>0.3334151208400726</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4400000000000001</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5003138184547424</v>
+        <v>0.5003139972686768</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.4284367263317108</v>
+        <v>0.428436815738678</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.16</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.2124502211809158</v>
+        <v>0.2124512940645218</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.4235819280147552</v>
+        <v>0.4235823154449463</v>
       </c>
       <c r="JB6" t="n">
         <v>0.1600000000000001</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.3893640637397766</v>
+        <v>0.389364093542099</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3644724190235138</v>
+        <v>0.3644721806049347</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4570061266422272</v>
+        <v>0.4570060670375824</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3272684812545776</v>
+        <v>0.3272684514522552</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.7199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3465485274791718</v>
+        <v>0.3465483784675598</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2246038317680359</v>
+        <v>0.2246039658784866</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.3207010328769684</v>
+        <v>0.320701003074646</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4666726589202881</v>
+        <v>0.4666725993156433</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.1199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.3124177157878876</v>
+        <v>0.3124176263809204</v>
       </c>
       <c r="JB19" t="n">
         <v>0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3402253091335297</v>
+        <v>0.3402253389358521</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.6286754608154297</v>
+        <v>0.6286754012107849</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.757672905921936</v>
+        <v>0.7576733231544495</v>
       </c>
       <c r="JB23" t="n">
         <v>0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3467929661273956</v>
+        <v>0.3467930257320404</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3769911527633667</v>
+        <v>0.3769911825656891</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3560411334037781</v>
+        <v>0.3560410141944885</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.6990740299224854</v>
+        <v>0.6990740895271301</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3389512896537781</v>
+        <v>0.3389514088630676</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4007908701896667</v>
+        <v>0.400790810585022</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2456454634666443</v>
+        <v>0.2456454038619995</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.5146462321281433</v>
+        <v>0.5146461725234985</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.7677150964736938</v>
+        <v>0.7677155137062073</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.9504247903823853</v>
+        <v>0.9504242539405823</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4715000987052917</v>
+        <v>0.4714983403682709</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.6933432221412659</v>
+        <v>0.6933415532112122</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2600908875465393</v>
+        <v>0.2600894868373871</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5216060280799866</v>
+        <v>0.5216042399406433</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.16</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.6386104822158813</v>
+        <v>0.6386092901229858</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.16</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.8743221759796143</v>
+        <v>0.8743208050727844</v>
       </c>
       <c r="JB43" t="n">
         <v>0.1199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.9118449687957764</v>
+        <v>0.9118436574935913</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.8282283544540405</v>
+        <v>0.8282256126403809</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.607400119304657</v>
+        <v>0.6073963046073914</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.03757831454277039</v>
+        <v>0.03757843747735023</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.128441646695137</v>
+        <v>0.1284417510032654</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.2431824505329132</v>
+        <v>0.2431826889514923</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3690527975559235</v>
+        <v>0.3690524101257324</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.09341432154178619</v>
+        <v>0.09341433644294739</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2534955739974976</v>
+        <v>0.2534953951835632</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.3762439489364624</v>
+        <v>0.3762441575527191</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3615978062152863</v>
+        <v>0.3615976870059967</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.651965320110321</v>
+        <v>0.6519656777381897</v>
       </c>
       <c r="JB55" t="n">
         <v>0.1600000000000001</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.5263922810554504</v>
+        <v>0.526391863822937</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2178253084421158</v>
+        <v>0.2178255468606949</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.9727963805198669</v>
+        <v>0.9727957248687744</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.1924462020397186</v>
+        <v>0.1924443244934082</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.06199027970433235</v>
+        <v>0.06199043989181519</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3139770328998566</v>
+        <v>0.3139772117137909</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.133549302816391</v>
+        <v>0.1335493624210358</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.2581522166728973</v>
+        <v>0.2581519484519958</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.8350391387939453</v>
+        <v>0.8350386619567871</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.9504045844078064</v>
+        <v>0.9504035711288452</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.9551312327384949</v>
+        <v>0.9551303386688232</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.05566310882568359</v>
+        <v>0.05566303431987762</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.02230958081781864</v>
+        <v>0.02230953425168991</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.0681685134768486</v>
+        <v>0.06816841661930084</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.1748306006193161</v>
+        <v>0.1748308092355728</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1063151508569717</v>
+        <v>0.1063152700662613</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1628269851207733</v>
+        <v>0.1628272831439972</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1530886441469193</v>
+        <v>0.1530888974666595</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.1904149502515793</v>
+        <v>0.1904150992631912</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.2932034134864807</v>
+        <v>0.293203741312027</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3553952276706696</v>
+        <v>0.3553954362869263</v>
       </c>
       <c r="JB77" t="n">
         <v>0.4399999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.127453550696373</v>
+        <v>0.1274538785219193</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.7941673398017883</v>
+        <v>0.794167160987854</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.7187919616699219</v>
+        <v>0.7187917828559875</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.1111945584416389</v>
+        <v>0.1111946702003479</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.3716713190078735</v>
+        <v>0.3716716468334198</v>
       </c>
       <c r="JB82" t="n">
         <v>0.4399999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6931749582290649</v>
+        <v>0.6931747198104858</v>
       </c>
       <c r="JB83" t="n">
         <v>0.1600000000000001</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.520207405090332</v>
+        <v>0.5202068686485291</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1533606052398682</v>
+        <v>0.1533608585596085</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.2409333139657974</v>
+        <v>0.2409335970878601</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.4776118397712708</v>
+        <v>0.4776119291782379</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.3957023322582245</v>
+        <v>0.3957024812698364</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.673356831073761</v>
+        <v>0.6733565330505371</v>
       </c>
       <c r="JB89" t="n">
         <v>0.5799999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2536543607711792</v>
+        <v>0.2536544799804688</v>
       </c>
       <c r="JB90" t="n">
         <v>0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5524531006813049</v>
+        <v>0.5524532794952393</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.6545088291168213</v>
+        <v>0.6545082926750183</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.08413980156183243</v>
+        <v>0.08414006233215332</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.8305273056030273</v>
+        <v>0.8305245041847229</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.05593381449580193</v>
+        <v>0.05593401566147804</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.1374646872282028</v>
+        <v>0.1374649703502655</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2275641262531281</v>
+        <v>0.2275642901659012</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3994114995002747</v>
+        <v>0.3994117975234985</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1130324229598045</v>
+        <v>0.1130324974656105</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4539130926132202</v>
+        <v>0.4539129436016083</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1283512562513351</v>
+        <v>0.1283514499664307</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.6326693296432495</v>
+        <v>0.632669985294342</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.883162796497345</v>
+        <v>0.8831625580787659</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.4758367538452148</v>
+        <v>0.4758368730545044</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1619477570056915</v>
+        <v>0.1619480103254318</v>
       </c>
       <c r="JB105" t="n">
         <v>0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3882326483726501</v>
+        <v>0.3882328569889069</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.04950717091560364</v>
+        <v>0.0495072714984417</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3260453045368195</v>
+        <v>0.3260453939437866</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.7767101526260376</v>
+        <v>0.7767106890678406</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3583757877349854</v>
+        <v>0.3583759367465973</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.7261248230934143</v>
+        <v>0.7261247038841248</v>
       </c>
       <c r="JB111" t="n">
         <v>0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.06479696929454803</v>
+        <v>0.06479712575674057</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.4512325525283813</v>
+        <v>0.4512326419353485</v>
       </c>
       <c r="JB113" t="n">
         <v>0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.7126254439353943</v>
+        <v>0.7126262187957764</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4403885900974274</v>
+        <v>0.4403887093067169</v>
       </c>
       <c r="JB115" t="n">
         <v>0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4690607786178589</v>
+        <v>0.4690611064434052</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.4713209569454193</v>
+        <v>0.4713212549686432</v>
       </c>
       <c r="JB117" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2627516686916351</v>
+        <v>0.2627521157264709</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2114299237728119</v>
+        <v>0.2114302963018417</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3735687136650085</v>
+        <v>0.3735691010951996</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3009952008724213</v>
+        <v>0.3009955585002899</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4682797491550446</v>
+        <v>0.4682799577713013</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.423176109790802</v>
+        <v>0.4231763482093811</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4014048874378204</v>
+        <v>0.4014049768447876</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.4399999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.3826521039009094</v>
+        <v>0.3826521635055542</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1600000000000001</v>
